--- a/diseases/d088/2020-2025.xlsx
+++ b/diseases/d088/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1159,9 +1156,6 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
